--- a/Proyectos/Fundamentos-de-Construccion/Solucion/MEMORIAS DE CALCULO - CDI TESALIA MODULO 1.xlsx
+++ b/Proyectos/Fundamentos-de-Construccion/Solucion/MEMORIAS DE CALCULO - CDI TESALIA MODULO 1.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G12"/>
+  <dimension ref="B1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -629,7 +629,7 @@
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Excavacion masiva plataforma de cimentacion</t>
+          <t>Excavacion plataforma e=0.55</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
@@ -649,38 +649,60 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Zanjas cimentacion a 1.5m (prof. extra 0.95)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>43.377</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="10" t="n">
-        <v>118.914</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="11" t="inlineStr">
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="10" t="n">
+        <v>162.291</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>OBSERVACIONES: cantidades obtenidas de planos arquitectonico/estructural DWG del CDI Tesalia.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Elaboro</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Reviso</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Aprobo</t>
         </is>
@@ -1811,7 +1833,7 @@
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Columnetas c/3 m (58 und x H=2.90)</t>
+          <t>Columnetas c/1.5m (116 und x H=2.90)</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
@@ -1826,10 +1848,10 @@
         <v>2.9</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>168.2</v>
+        <v>336.4</v>
       </c>
     </row>
     <row r="8">
@@ -1843,7 +1865,7 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="10" t="n">
-        <v>168.2</v>
+        <v>336.4</v>
       </c>
     </row>
     <row r="10">
@@ -2756,7 +2778,7 @@
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Long. 4#3 (kg)</t>
+          <t>Long. 2 Ø1/2" (#4) vertical (kg)</t>
         </is>
       </c>
       <c r="C7" s="5" t="n"/>
@@ -2764,13 +2786,13 @@
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="13" t="n">
-        <v>376.8</v>
+        <v>668.8</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Estribos #2 c/0.20 (kg)</t>
+          <t>Estribos/ganchos #2 (1/4") (kg)</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
@@ -2778,7 +2800,7 @@
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="13" t="n">
-        <v>105.1</v>
+        <v>269.1</v>
       </c>
     </row>
     <row r="9">
@@ -2792,7 +2814,7 @@
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="13" t="n">
-        <v>481.9</v>
+        <v>937.9</v>
       </c>
     </row>
     <row r="10">
@@ -2806,7 +2828,7 @@
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="13" t="n">
-        <v>530.1</v>
+        <v>1031.7</v>
       </c>
     </row>
     <row r="11">
@@ -2820,7 +2842,7 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="14" t="n">
-        <v>530.1</v>
+        <v>1031.7</v>
       </c>
     </row>
   </sheetData>
@@ -2963,14 +2985,14 @@
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Capa de subbase granular bajo placa e=0.15</t>
+          <t>Colchon granular 0.30 m bajo placa (plano: min 0.30)</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
         <v>9.85</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>21.95</v>
@@ -2979,7 +3001,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>32.431</v>
+        <v>64.86199999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2993,7 +3015,7 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="10" t="n">
-        <v>32.431</v>
+        <v>64.86199999999999</v>
       </c>
     </row>
     <row r="10">
@@ -3311,7 +3333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G13"/>
+  <dimension ref="B1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3431,80 +3453,58 @@
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Afinado de zanjas vigas long. A,B</t>
+          <t>Afinado fondo de zanjas</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>19.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>6.336</v>
+        <v>6.849</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Afinado de zanjas vigas transv. 1-4 (luz libre)</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>5.84</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="10" t="n">
-        <v>12.176</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="10" t="n">
+        <v>6.849</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>OBSERVACIONES: cantidades obtenidas de planos arquitectonico/estructural DWG del CDI Tesalia.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Elaboro</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Reviso</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Aprobo</t>
         </is>

--- a/Proyectos/Fundamentos-de-Construccion/Solucion/MEMORIAS DE CALCULO - CDI TESALIA MODULO 1.xlsx
+++ b/Proyectos/Fundamentos-de-Construccion/Solucion/MEMORIAS DE CALCULO - CDI TESALIA MODULO 1.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G13"/>
+  <dimension ref="B1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -629,80 +629,102 @@
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Excavacion plataforma e=0.55</t>
+          <t>Pozos zapatas Z-1 (2.30x2.30) a 1.5m</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>9.85</v>
+        <v>2.3</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.55</v>
+        <v>2.3</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>21.95</v>
+        <v>1.5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>118.914</v>
+        <v>31.74</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Zanjas cimentacion a 1.5m (prof. extra 0.95)</t>
+          <t>Pozos zapatas Z-2 (2.15x2.15) a 1.5m</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>27.735</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Zanjas de vigas de cimentacion a 1.5m</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="F8" s="6" t="n">
+      <c r="D9" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="F9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>43.377</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="8" t="inlineStr">
+      <c r="G9" s="7" t="n">
+        <v>52.65</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="10" t="n">
-        <v>162.291</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="10" t="n">
+        <v>112.125</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>OBSERVACIONES: cantidades obtenidas de planos arquitectonico/estructural DWG del CDI Tesalia.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Elaboro</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Reviso</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Aprobo</t>
         </is>
@@ -1615,7 +1637,7 @@
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Area bruta de muros (L=173.60 x H=2.90)</t>
+          <t>Area bruta de muros (L=173.60 x H=3.00)</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
@@ -1627,13 +1649,13 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>503.44</v>
+        <v>520.8</v>
       </c>
     </row>
     <row r="8">
@@ -1651,13 +1673,13 @@
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>-0.2</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-100.688</v>
+        <v>-104.16</v>
       </c>
     </row>
     <row r="9">
@@ -1671,7 +1693,7 @@
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="10" t="n">
-        <v>402.752</v>
+        <v>416.64</v>
       </c>
     </row>
     <row r="11">
@@ -1833,7 +1855,7 @@
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Columnetas c/1.5m (116 und x H=2.90)</t>
+          <t>Columnetas c/1.5m (116 und x H=3.00)</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
@@ -1845,13 +1867,13 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>116</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>336.4</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8">
@@ -1865,7 +1887,7 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="10" t="n">
-        <v>336.4</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -2031,7 +2053,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>402.75</v>
+        <v>416.64</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -2045,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>261.788</v>
+        <v>270.816</v>
       </c>
     </row>
     <row r="8">
@@ -2059,7 +2081,7 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="10" t="n">
-        <v>261.788</v>
+        <v>270.816</v>
       </c>
     </row>
     <row r="10">
@@ -2396,7 +2418,7 @@
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Long. 10col x (2#6+2#7) L=5.95 (kg)</t>
+          <t>Long. 8 col x (2#6+2#7) L=5.95 (kg)</t>
         </is>
       </c>
       <c r="C7" s="5" t="n"/>
@@ -2404,13 +2426,13 @@
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="13" t="n">
-        <v>628</v>
+        <v>502.4</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Estribos #2 c/0.20 (kg)</t>
+          <t>Estribos #2 c/0.20 (4 col 0.40 + 4 col 0.50) (kg)</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
@@ -2418,7 +2440,7 @@
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="13" t="n">
-        <v>91.90000000000001</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="9">
@@ -2432,7 +2454,7 @@
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="13" t="n">
-        <v>719.8</v>
+        <v>585.7</v>
       </c>
     </row>
     <row r="10">
@@ -2446,7 +2468,7 @@
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="13" t="n">
-        <v>791.8</v>
+        <v>644.2</v>
       </c>
     </row>
     <row r="11">
@@ -2460,7 +2482,7 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="14" t="n">
-        <v>791.8</v>
+        <v>644.2</v>
       </c>
     </row>
   </sheetData>
@@ -2786,7 +2808,7 @@
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="13" t="n">
-        <v>668.8</v>
+        <v>691.8</v>
       </c>
     </row>
     <row r="8">
@@ -2800,7 +2822,7 @@
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="13" t="n">
-        <v>269.1</v>
+        <v>278.4</v>
       </c>
     </row>
     <row r="9">
@@ -2814,7 +2836,7 @@
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="13" t="n">
-        <v>937.9</v>
+        <v>970.2</v>
       </c>
     </row>
     <row r="10">
@@ -2828,7 +2850,7 @@
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="13" t="n">
-        <v>1031.7</v>
+        <v>1067.2</v>
       </c>
     </row>
     <row r="11">
@@ -2842,7 +2864,7 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="14" t="n">
-        <v>1031.7</v>
+        <v>1067.2</v>
       </c>
     </row>
   </sheetData>
@@ -3453,23 +3475,25 @@
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Afinado fondo de zanjas</t>
+          <t>Afinado fondo de pozos y zanjas e=0.10</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>0.15</v>
+        <v>74.75</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>76.09999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>6.849</v>
+        <v>7.475</v>
       </c>
     </row>
     <row r="8">
@@ -3483,7 +3507,7 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="10" t="n">
-        <v>6.849</v>
+        <v>7.475</v>
       </c>
     </row>
     <row r="10">
@@ -4343,7 +4367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G12"/>
+  <dimension ref="B1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4463,58 +4487,80 @@
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Columnas tipo 0.40x0.40 h=4.90 (10 und)</t>
+          <t>Columnas 0.50x0.50 h=4.90 (4 und, sobre Z-1)</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>4.9</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>7.84</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Columnas 0.40x0.40 h=4.90 (4 und, sobre Z-2)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>3.136</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="10" t="n">
-        <v>7.84</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="11" t="inlineStr">
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="10" t="n">
+        <v>8.036</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>OBSERVACIONES: cantidades obtenidas de planos arquitectonico/estructural DWG del CDI Tesalia.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Elaboro</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Reviso</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Aprobo</t>
         </is>
